--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_4.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4565 +469,6330 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:51.431</t>
+          <t>2026-05-29 09:34:53.997</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421673288</v>
+        <v>1780022092662</v>
       </c>
       <c r="C2" t="n">
-        <v>88207</v>
+        <v>83904</v>
       </c>
       <c r="D2" t="n">
-        <v>-321.38</v>
+        <v>3507.09</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>785</v>
+        <v>1599</v>
       </c>
       <c r="G2" t="n">
-        <v>83.08</v>
+        <v>288.57</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="L2" t="n">
+        <v>107</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.708</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:51.472</t>
+          <t>2026-05-29 09:34:54.178</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421673489</v>
+        <v>1780022092862</v>
       </c>
       <c r="C3" t="n">
-        <v>88400</v>
+        <v>84006</v>
       </c>
       <c r="D3" t="n">
-        <v>-112.31</v>
+        <v>3433.73</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>785</v>
+        <v>1599</v>
       </c>
       <c r="G3" t="n">
-        <v>83.08</v>
+        <v>288.57</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1315</v>
+      </c>
+      <c r="L3" t="n">
+        <v>113</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:51.472</t>
+          <t>2026-05-29 09:34:54.214</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421673691</v>
+        <v>1780022093062</v>
       </c>
       <c r="C4" t="n">
-        <v>88614</v>
+        <v>84107</v>
       </c>
       <c r="D4" t="n">
-        <v>107.3</v>
+        <v>3363.04</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>785</v>
+        <v>1599</v>
       </c>
       <c r="G4" t="n">
-        <v>83.08</v>
+        <v>288.57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L4" t="n">
+        <v>107</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:51.890</t>
+          <t>2026-05-29 09:34:54.693</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421673892</v>
+        <v>1780022093281</v>
       </c>
       <c r="C5" t="n">
-        <v>88829</v>
+        <v>84176</v>
       </c>
       <c r="D5" t="n">
-        <v>316.94</v>
+        <v>3263.89</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>846</v>
+        <v>1599</v>
       </c>
       <c r="G5" t="n">
-        <v>77.87</v>
+        <v>288.57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1411</v>
+      </c>
+      <c r="L5" t="n">
+        <v>111</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.602</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:51.892</t>
+          <t>2026-05-29 09:34:54.694</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421674093</v>
+        <v>1780022093481</v>
       </c>
       <c r="C6" t="n">
-        <v>88319</v>
+        <v>84117</v>
       </c>
       <c r="D6" t="n">
-        <v>-208.91</v>
+        <v>3041.7</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>846</v>
+        <v>1599</v>
       </c>
       <c r="G6" t="n">
-        <v>77.87</v>
+        <v>288.57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1212</v>
+      </c>
+      <c r="L6" t="n">
+        <v>105</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:52.296</t>
+          <t>2026-05-29 09:34:54.696</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421674295</v>
+        <v>1780022093681</v>
       </c>
       <c r="C7" t="n">
-        <v>88532</v>
+        <v>83430</v>
       </c>
       <c r="D7" t="n">
-        <v>14.54</v>
+        <v>2202.61</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>846</v>
+        <v>1599</v>
       </c>
       <c r="G7" t="n">
-        <v>77.87</v>
+        <v>288.57</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L7" t="n">
+        <v>109</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:52.325</t>
+          <t>2026-05-29 09:34:54.946</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421674496</v>
+        <v>1780022093881</v>
       </c>
       <c r="C8" t="n">
-        <v>88785</v>
+        <v>83647</v>
       </c>
       <c r="D8" t="n">
-        <v>266.81</v>
+        <v>2309.48</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>725</v>
+        <v>1599</v>
       </c>
       <c r="G8" t="n">
-        <v>78.36</v>
+        <v>288.57</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1064</v>
+      </c>
+      <c r="L8" t="n">
+        <v>110</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:52.685</t>
+          <t>2026-05-29 09:34:54.947</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421674698</v>
+        <v>1780022094081</v>
       </c>
       <c r="C9" t="n">
-        <v>88722</v>
+        <v>83568</v>
       </c>
       <c r="D9" t="n">
-        <v>190.47</v>
+        <v>2115.01</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>725</v>
+        <v>1599</v>
       </c>
       <c r="G9" t="n">
-        <v>78.36</v>
+        <v>288.57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>865</v>
+      </c>
+      <c r="L9" t="n">
+        <v>112</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:52.685</t>
+          <t>2026-05-29 09:34:55.600</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421674899</v>
+        <v>1780022094281</v>
       </c>
       <c r="C10" t="n">
-        <v>88385</v>
+        <v>82929</v>
       </c>
       <c r="D10" t="n">
-        <v>-156.05</v>
+        <v>1370.26</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>725</v>
+        <v>1599</v>
       </c>
       <c r="G10" t="n">
-        <v>78.36</v>
+        <v>288.57</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1318</v>
+      </c>
+      <c r="L10" t="n">
+        <v>112</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.095</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:53.134</t>
+          <t>2026-05-29 09:34:55.601</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421675100</v>
+        <v>1780022094481</v>
       </c>
       <c r="C11" t="n">
-        <v>88536</v>
+        <v>83091</v>
       </c>
       <c r="D11" t="n">
-        <v>2.75</v>
+        <v>1463.74</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>725</v>
+        <v>1599</v>
       </c>
       <c r="G11" t="n">
-        <v>78.36</v>
+        <v>288.57</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1119</v>
+      </c>
+      <c r="L11" t="n">
+        <v>106</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.921</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:53.135</t>
+          <t>2026-05-29 09:34:56.024</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421675302</v>
+        <v>1780022094681</v>
       </c>
       <c r="C12" t="n">
-        <v>88703</v>
+        <v>83022</v>
       </c>
       <c r="D12" t="n">
-        <v>169.61</v>
+        <v>1321.56</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>806</v>
+        <v>1599</v>
       </c>
       <c r="G12" t="n">
-        <v>80.20999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1343</v>
+      </c>
+      <c r="L12" t="n">
+        <v>114</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:53.495</t>
+          <t>2026-05-29 09:34:56.058</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421675503</v>
+        <v>1780022094881</v>
       </c>
       <c r="C13" t="n">
-        <v>88439</v>
+        <v>82561</v>
       </c>
       <c r="D13" t="n">
-        <v>-102.87</v>
+        <v>794.48</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>806</v>
+        <v>1599</v>
       </c>
       <c r="G13" t="n">
-        <v>80.20999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1176</v>
+      </c>
+      <c r="L13" t="n">
+        <v>111</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:53.496</t>
+          <t>2026-05-29 09:34:56.060</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421675705</v>
+        <v>1780022095100</v>
       </c>
       <c r="C14" t="n">
-        <v>88281</v>
+        <v>82777</v>
       </c>
       <c r="D14" t="n">
-        <v>-255.73</v>
+        <v>970.76</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>806</v>
+        <v>1599</v>
       </c>
       <c r="G14" t="n">
-        <v>80.20999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>959</v>
+      </c>
+      <c r="L14" t="n">
+        <v>113</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.929</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:54.055</t>
+          <t>2026-05-29 09:34:56.342</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421675906</v>
+        <v>1780022095300</v>
       </c>
       <c r="C15" t="n">
-        <v>88436</v>
+        <v>83065</v>
       </c>
       <c r="D15" t="n">
-        <v>-87.94</v>
+        <v>1210.22</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>806</v>
+        <v>1599</v>
       </c>
       <c r="G15" t="n">
-        <v>80.20999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1042</v>
+      </c>
+      <c r="L15" t="n">
+        <v>114</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.498</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:54.056</t>
+          <t>2026-05-29 09:34:56.344</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421676107</v>
+        <v>1780022095500</v>
       </c>
       <c r="C16" t="n">
-        <v>88660</v>
+        <v>82456</v>
       </c>
       <c r="D16" t="n">
-        <v>140.46</v>
+        <v>540.71</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>805</v>
+        <v>3018</v>
       </c>
       <c r="G16" t="n">
-        <v>78.41</v>
+        <v>288.57</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>843</v>
+      </c>
+      <c r="L16" t="n">
+        <v>118</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.923</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:54.074</t>
+          <t>2026-05-29 09:34:56.783</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421676309</v>
+        <v>1780022095700</v>
       </c>
       <c r="C17" t="n">
-        <v>88724</v>
+        <v>82692</v>
       </c>
       <c r="D17" t="n">
-        <v>197.43</v>
+        <v>749.67</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>805</v>
+        <v>3018</v>
       </c>
       <c r="G17" t="n">
-        <v>78.41</v>
+        <v>288.57</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1082</v>
+      </c>
+      <c r="L17" t="n">
+        <v>113</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.023</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:54.324</t>
+          <t>2026-05-29 09:34:56.818</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421676510</v>
+        <v>1780022095900</v>
       </c>
       <c r="C18" t="n">
-        <v>88291</v>
+        <v>82963</v>
       </c>
       <c r="D18" t="n">
-        <v>-245.44</v>
+        <v>983.1900000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>805</v>
+        <v>3018</v>
       </c>
       <c r="G18" t="n">
-        <v>78.41</v>
+        <v>288.57</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>917</v>
+      </c>
+      <c r="L18" t="n">
+        <v>107</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.708</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:54.763</t>
+          <t>2026-05-29 09:34:57.467</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421676712</v>
+        <v>1780022096100</v>
       </c>
       <c r="C19" t="n">
-        <v>88526</v>
+        <v>82460</v>
       </c>
       <c r="D19" t="n">
-        <v>1.83</v>
+        <v>431.03</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F19" t="n">
-        <v>805</v>
+        <v>560</v>
       </c>
       <c r="G19" t="n">
-        <v>78.41</v>
+        <v>306.73</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1366</v>
+      </c>
+      <c r="L19" t="n">
+        <v>107</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:54.782</t>
+          <t>2026-05-29 09:34:57.478</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421676913</v>
+        <v>1780022096300</v>
       </c>
       <c r="C20" t="n">
-        <v>88747</v>
+        <v>82475</v>
       </c>
       <c r="D20" t="n">
-        <v>222.74</v>
+        <v>424.48</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>766</v>
+        <v>560</v>
       </c>
       <c r="G20" t="n">
-        <v>74.68000000000001</v>
+        <v>306.73</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1177</v>
+      </c>
+      <c r="L20" t="n">
+        <v>106</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:55.129</t>
+          <t>2026-05-29 09:34:57.480</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421677115</v>
+        <v>1780022096500</v>
       </c>
       <c r="C21" t="n">
-        <v>88360</v>
+        <v>82790</v>
       </c>
       <c r="D21" t="n">
-        <v>-175.39</v>
+        <v>718.25</v>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F21" t="n">
-        <v>766</v>
+        <v>560</v>
       </c>
       <c r="G21" t="n">
-        <v>74.68000000000001</v>
+        <v>306.73</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K21" t="n">
+        <v>979</v>
+      </c>
+      <c r="L21" t="n">
+        <v>103</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.711</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:55.129</t>
+          <t>2026-05-29 09:34:57.763</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421677316</v>
+        <v>1780022096700</v>
       </c>
       <c r="C22" t="n">
-        <v>88448</v>
+        <v>83034</v>
       </c>
       <c r="D22" t="n">
-        <v>-78.62</v>
+        <v>926.34</v>
       </c>
       <c r="E22" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>766</v>
+        <v>680</v>
       </c>
       <c r="G22" t="n">
-        <v>74.68000000000001</v>
+        <v>286</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1062</v>
+      </c>
+      <c r="L22" t="n">
+        <v>108</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.168</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:55.698</t>
+          <t>2026-05-29 09:34:58.554</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421677517</v>
+        <v>1780022096900</v>
       </c>
       <c r="C23" t="n">
-        <v>88608</v>
+        <v>82786</v>
       </c>
       <c r="D23" t="n">
-        <v>85.31</v>
+        <v>632.02</v>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
-        <v>766</v>
+        <v>680</v>
       </c>
       <c r="G23" t="n">
-        <v>74.68000000000001</v>
+        <v>286</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1653</v>
+      </c>
+      <c r="L23" t="n">
+        <v>107</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:55.736</t>
+          <t>2026-05-29 09:34:58.556</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421677719</v>
+        <v>1780022097119</v>
       </c>
       <c r="C24" t="n">
-        <v>88836</v>
+        <v>83163</v>
       </c>
       <c r="D24" t="n">
-        <v>309.04</v>
+        <v>977.42</v>
       </c>
       <c r="E24" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F24" t="n">
-        <v>765</v>
+        <v>499</v>
       </c>
       <c r="G24" t="n">
-        <v>73.58</v>
+        <v>283.51</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1436</v>
+      </c>
+      <c r="L24" t="n">
+        <v>117</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.914</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:55.959</t>
+          <t>2026-05-29 09:34:59.063</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421677920</v>
+        <v>1780022097319</v>
       </c>
       <c r="C25" t="n">
-        <v>88322</v>
+        <v>83241</v>
       </c>
       <c r="D25" t="n">
-        <v>-220.41</v>
+        <v>1006.55</v>
       </c>
       <c r="E25" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F25" t="n">
-        <v>765</v>
+        <v>499</v>
       </c>
       <c r="G25" t="n">
-        <v>73.58</v>
+        <v>283.51</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1743</v>
+      </c>
+      <c r="L25" t="n">
+        <v>109</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:55.960</t>
+          <t>2026-05-29 09:34:59.064</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421678122</v>
+        <v>1780022097519</v>
       </c>
       <c r="C26" t="n">
-        <v>88519</v>
+        <v>82890</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.39</v>
+        <v>605.22</v>
       </c>
       <c r="E26" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F26" t="n">
-        <v>765</v>
+        <v>499</v>
       </c>
       <c r="G26" t="n">
-        <v>73.58</v>
+        <v>283.51</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1544</v>
+      </c>
+      <c r="L26" t="n">
+        <v>109</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.735</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:56.409</t>
+          <t>2026-05-29 09:34:59.081</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421678323</v>
+        <v>1780022097719</v>
       </c>
       <c r="C27" t="n">
-        <v>88770</v>
+        <v>83048</v>
       </c>
       <c r="D27" t="n">
-        <v>239.23</v>
+        <v>732.96</v>
       </c>
       <c r="E27" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="F27" t="n">
-        <v>685</v>
+        <v>499</v>
       </c>
       <c r="G27" t="n">
-        <v>77.75</v>
+        <v>283.51</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1360</v>
+      </c>
+      <c r="L27" t="n">
+        <v>105</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:56.448</t>
+          <t>2026-05-29 09:34:59.082</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421678524</v>
+        <v>1780022097919</v>
       </c>
       <c r="C28" t="n">
-        <v>88292</v>
+        <v>83221</v>
       </c>
       <c r="D28" t="n">
-        <v>-250.73</v>
+        <v>869.3099999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F28" t="n">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="G28" t="n">
-        <v>77.75</v>
+        <v>284.86</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L28" t="n">
+        <v>107</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.695</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:56.790</t>
+          <t>2026-05-29 09:34:59.538</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421678726</v>
+        <v>1780022098119</v>
       </c>
       <c r="C29" t="n">
-        <v>88387</v>
+        <v>82620</v>
       </c>
       <c r="D29" t="n">
-        <v>-143.2</v>
+        <v>224.85</v>
       </c>
       <c r="E29" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F29" t="n">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="G29" t="n">
-        <v>77.75</v>
+        <v>284.86</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L29" t="n">
+        <v>106</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.056</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:56.791</t>
+          <t>2026-05-29 09:34:59.540</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421678927</v>
+        <v>1780022098319</v>
       </c>
       <c r="C30" t="n">
-        <v>88558</v>
+        <v>82736</v>
       </c>
       <c r="D30" t="n">
-        <v>34.96</v>
+        <v>329.61</v>
       </c>
       <c r="E30" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F30" t="n">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="G30" t="n">
-        <v>77.75</v>
+        <v>284.86</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1220</v>
+      </c>
+      <c r="L30" t="n">
+        <v>105</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.847</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:57.196</t>
+          <t>2026-05-29 09:34:59.771</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421679129</v>
+        <v>1780022098519</v>
       </c>
       <c r="C31" t="n">
-        <v>88410</v>
+        <v>83007</v>
       </c>
       <c r="D31" t="n">
-        <v>-114.78</v>
+        <v>584.13</v>
       </c>
       <c r="E31" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="F31" t="n">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G31" t="n">
-        <v>74.62</v>
+        <v>284.86</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1251</v>
+      </c>
+      <c r="L31" t="n">
+        <v>107</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.098</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:57.197</t>
+          <t>2026-05-29 09:34:59.773</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421679330</v>
+        <v>1780022098719</v>
       </c>
       <c r="C32" t="n">
-        <v>88255</v>
+        <v>82341</v>
       </c>
       <c r="D32" t="n">
-        <v>-264.04</v>
+        <v>-111.08</v>
       </c>
       <c r="E32" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F32" t="n">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="G32" t="n">
-        <v>74.62</v>
+        <v>278.09</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1052</v>
+      </c>
+      <c r="L32" t="n">
+        <v>110</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:57.719</t>
+          <t>2026-05-29 09:34:59.774</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421679531</v>
+        <v>1780022098919</v>
       </c>
       <c r="C33" t="n">
-        <v>88454</v>
+        <v>82540</v>
       </c>
       <c r="D33" t="n">
-        <v>-51.84</v>
+        <v>93.47</v>
       </c>
       <c r="E33" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F33" t="n">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="G33" t="n">
-        <v>74.62</v>
+        <v>278.09</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K33" t="n">
+        <v>854</v>
+      </c>
+      <c r="L33" t="n">
+        <v>104</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.026</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:57.737</t>
+          <t>2026-05-29 09:35:00.126</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421679733</v>
+        <v>1780022099138</v>
       </c>
       <c r="C34" t="n">
-        <v>88573</v>
+        <v>82879</v>
       </c>
       <c r="D34" t="n">
-        <v>69.75</v>
+        <v>427.8</v>
       </c>
       <c r="E34" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F34" t="n">
-        <v>624</v>
+        <v>740</v>
       </c>
       <c r="G34" t="n">
-        <v>65.26000000000001</v>
+        <v>278.09</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K34" t="n">
+        <v>986</v>
+      </c>
+      <c r="L34" t="n">
+        <v>108</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.591</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:57.737</t>
+          <t>2026-05-29 09:35:00.497</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421679934</v>
+        <v>1780022099338</v>
       </c>
       <c r="C35" t="n">
-        <v>87989</v>
+        <v>81548</v>
       </c>
       <c r="D35" t="n">
-        <v>-517.74</v>
+        <v>-924.59</v>
       </c>
       <c r="E35" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F35" t="n">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="G35" t="n">
-        <v>65.26000000000001</v>
+        <v>221.54</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1158</v>
+      </c>
+      <c r="L35" t="n">
+        <v>108</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.578</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:58.003</t>
+          <t>2026-05-29 09:35:00.498</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421680136</v>
+        <v>1780022099538</v>
       </c>
       <c r="C36" t="n">
-        <v>88175</v>
+        <v>80884</v>
       </c>
       <c r="D36" t="n">
-        <v>-305.85</v>
+        <v>-1542.36</v>
       </c>
       <c r="E36" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F36" t="n">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="G36" t="n">
-        <v>65.26000000000001</v>
+        <v>221.54</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>959</v>
+      </c>
+      <c r="L36" t="n">
+        <v>109</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.754</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:58.408</t>
+          <t>2026-05-29 09:35:01.558</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421680337</v>
+        <v>1780022099738</v>
       </c>
       <c r="C37" t="n">
-        <v>88371</v>
+        <v>81853</v>
       </c>
       <c r="D37" t="n">
-        <v>-94.56</v>
+        <v>-496.24</v>
       </c>
       <c r="E37" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F37" t="n">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="G37" t="n">
-        <v>65.26000000000001</v>
+        <v>221.54</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1819</v>
+      </c>
+      <c r="L37" t="n">
+        <v>118</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:58.409</t>
+          <t>2026-05-29 09:35:01.560</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421680539</v>
+        <v>1780022099938</v>
       </c>
       <c r="C38" t="n">
-        <v>87842</v>
+        <v>82167</v>
       </c>
       <c r="D38" t="n">
-        <v>-618.83</v>
+        <v>-157.43</v>
       </c>
       <c r="E38" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F38" t="n">
-        <v>726</v>
+        <v>639</v>
       </c>
       <c r="G38" t="n">
-        <v>64.73</v>
+        <v>221.54</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1620</v>
+      </c>
+      <c r="L38" t="n">
+        <v>113</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.064</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:58.841</t>
+          <t>2026-05-29 09:35:02.009</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421680740</v>
+        <v>1780022100138</v>
       </c>
       <c r="C39" t="n">
-        <v>88130</v>
+        <v>81937</v>
       </c>
       <c r="D39" t="n">
-        <v>-299.89</v>
+        <v>-379.56</v>
       </c>
       <c r="E39" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F39" t="n">
-        <v>726</v>
+        <v>639</v>
       </c>
       <c r="G39" t="n">
-        <v>64.73</v>
+        <v>221.54</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1870</v>
+      </c>
+      <c r="L39" t="n">
+        <v>118</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:58.842</t>
+          <t>2026-05-29 09:35:02.010</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421680941</v>
+        <v>1780022100338</v>
       </c>
       <c r="C40" t="n">
-        <v>88270</v>
+        <v>81852</v>
       </c>
       <c r="D40" t="n">
-        <v>-144.89</v>
+        <v>-445.58</v>
       </c>
       <c r="E40" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F40" t="n">
-        <v>726</v>
+        <v>639</v>
       </c>
       <c r="G40" t="n">
-        <v>64.73</v>
+        <v>221.54</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L40" t="n">
+        <v>113</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:59.257</t>
+          <t>2026-05-29 09:35:02.012</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421681143</v>
+        <v>1780022100538</v>
       </c>
       <c r="C41" t="n">
-        <v>88000</v>
+        <v>81898</v>
       </c>
       <c r="D41" t="n">
-        <v>-407.65</v>
+        <v>-377.3</v>
       </c>
       <c r="E41" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F41" t="n">
-        <v>604</v>
+        <v>639</v>
       </c>
       <c r="G41" t="n">
-        <v>68.84</v>
+        <v>221.54</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1473</v>
+      </c>
+      <c r="L41" t="n">
+        <v>104</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.919</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:59.258</t>
+          <t>2026-05-29 09:35:02.013</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421681344</v>
+        <v>1780022100738</v>
       </c>
       <c r="C42" t="n">
-        <v>88295</v>
+        <v>81618</v>
       </c>
       <c r="D42" t="n">
-        <v>-92.27</v>
+        <v>-638.4400000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F42" t="n">
-        <v>604</v>
+        <v>639</v>
       </c>
       <c r="G42" t="n">
-        <v>68.84</v>
+        <v>221.54</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1274</v>
+      </c>
+      <c r="L42" t="n">
+        <v>106</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.153</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:59.561</t>
+          <t>2026-05-29 09:35:03.033</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421681546</v>
+        <v>1780022100957</v>
       </c>
       <c r="C43" t="n">
-        <v>88837</v>
+        <v>81513</v>
       </c>
       <c r="D43" t="n">
-        <v>454.35</v>
+        <v>-711.51</v>
       </c>
       <c r="E43" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F43" t="n">
-        <v>523</v>
+        <v>639</v>
       </c>
       <c r="G43" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2075</v>
+      </c>
+      <c r="L43" t="n">
+        <v>107</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:59.563</t>
+          <t>2026-05-29 09:35:03.035</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421681747</v>
+        <v>1780022101157</v>
       </c>
       <c r="C44" t="n">
-        <v>89185</v>
+        <v>81853</v>
       </c>
       <c r="D44" t="n">
-        <v>779.63</v>
+        <v>-335.94</v>
       </c>
       <c r="E44" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F44" t="n">
-        <v>523</v>
+        <v>639</v>
       </c>
       <c r="G44" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1877</v>
+      </c>
+      <c r="L44" t="n">
+        <v>115</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.331</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:59.846</t>
+          <t>2026-05-29 09:35:03.036</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421681948</v>
+        <v>1780022101357</v>
       </c>
       <c r="C45" t="n">
-        <v>88637</v>
+        <v>81113</v>
       </c>
       <c r="D45" t="n">
-        <v>192.65</v>
+        <v>-1059.14</v>
       </c>
       <c r="E45" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F45" t="n">
-        <v>523</v>
+        <v>639</v>
       </c>
       <c r="G45" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1678</v>
+      </c>
+      <c r="L45" t="n">
+        <v>109</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.837</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:00.251</t>
+          <t>2026-05-29 09:35:03.037</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421682150</v>
+        <v>1780022101557</v>
       </c>
       <c r="C46" t="n">
-        <v>89625</v>
+        <v>81207</v>
       </c>
       <c r="D46" t="n">
-        <v>1171.01</v>
+        <v>-912.1900000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F46" t="n">
-        <v>523</v>
+        <v>639</v>
       </c>
       <c r="G46" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1479</v>
+      </c>
+      <c r="L46" t="n">
+        <v>104</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:00.252</t>
+          <t>2026-05-29 09:35:05.711</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421682351</v>
+        <v>1780022101757</v>
       </c>
       <c r="C47" t="n">
-        <v>89153</v>
+        <v>81352</v>
       </c>
       <c r="D47" t="n">
-        <v>640.46</v>
+        <v>-721.58</v>
       </c>
       <c r="E47" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F47" t="n">
-        <v>523</v>
+        <v>639</v>
       </c>
       <c r="G47" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3952</v>
+      </c>
+      <c r="L47" t="n">
+        <v>99</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.119</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:00.709</t>
+          <t>2026-05-29 09:35:05.712</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421682553</v>
+        <v>1780022101957</v>
       </c>
       <c r="C48" t="n">
-        <v>87900</v>
+        <v>80860</v>
       </c>
       <c r="D48" t="n">
-        <v>-644.5599999999999</v>
+        <v>-1177.5</v>
       </c>
       <c r="E48" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F48" t="n">
-        <v>523</v>
+        <v>639</v>
       </c>
       <c r="G48" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J48" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3754</v>
+      </c>
+      <c r="L48" t="n">
+        <v>107</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:00.710</t>
+          <t>2026-05-29 09:35:05.713</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421682754</v>
+        <v>1780022103636</v>
       </c>
       <c r="C49" t="n">
-        <v>87530</v>
+        <v>81539</v>
       </c>
       <c r="D49" t="n">
-        <v>-982.33</v>
+        <v>-439.62</v>
       </c>
       <c r="E49" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F49" t="n">
-        <v>523</v>
+        <v>639</v>
       </c>
       <c r="G49" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2076</v>
+      </c>
+      <c r="L49" t="n">
+        <v>113</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:01.115</t>
+          <t>2026-05-29 09:35:05.715</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421682955</v>
+        <v>1780022103836</v>
       </c>
       <c r="C50" t="n">
-        <v>87892</v>
+        <v>81106</v>
       </c>
       <c r="D50" t="n">
-        <v>-571.21</v>
+        <v>-850.64</v>
       </c>
       <c r="E50" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F50" t="n">
-        <v>523</v>
+        <v>4618</v>
       </c>
       <c r="G50" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1878</v>
+      </c>
+      <c r="L50" t="n">
+        <v>116</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.513</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:01.123</t>
+          <t>2026-05-29 09:35:05.717</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421683157</v>
+        <v>1780022104036</v>
       </c>
       <c r="C51" t="n">
-        <v>87920</v>
+        <v>81051</v>
       </c>
       <c r="D51" t="n">
-        <v>-514.65</v>
+        <v>-863.11</v>
       </c>
       <c r="E51" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F51" t="n">
-        <v>523</v>
+        <v>4618</v>
       </c>
       <c r="G51" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1680</v>
+      </c>
+      <c r="L51" t="n">
+        <v>113</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.324</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:01.486</t>
+          <t>2026-05-29 09:35:05.718</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421683358</v>
+        <v>1780022104236</v>
       </c>
       <c r="C52" t="n">
-        <v>87361</v>
+        <v>80958</v>
       </c>
       <c r="D52" t="n">
-        <v>-1047.92</v>
+        <v>-912.95</v>
       </c>
       <c r="E52" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F52" t="n">
-        <v>523</v>
+        <v>4618</v>
       </c>
       <c r="G52" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L52" t="n">
+        <v>112</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.718</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:01.490</t>
+          <t>2026-05-29 09:35:05.956</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421683560</v>
+        <v>1780022104436</v>
       </c>
       <c r="C53" t="n">
-        <v>87550</v>
+        <v>80927</v>
       </c>
       <c r="D53" t="n">
-        <v>-806.53</v>
+        <v>-898.3099999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F53" t="n">
-        <v>523</v>
+        <v>4618</v>
       </c>
       <c r="G53" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1519</v>
+      </c>
+      <c r="L53" t="n">
+        <v>114</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.082</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:01.518</t>
+          <t>2026-05-29 09:35:05.957</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421683761</v>
+        <v>1780022104636</v>
       </c>
       <c r="C54" t="n">
-        <v>87786</v>
+        <v>80868</v>
       </c>
       <c r="D54" t="n">
-        <v>-530.2</v>
+        <v>-912.39</v>
       </c>
       <c r="E54" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F54" t="n">
-        <v>523</v>
+        <v>4618</v>
       </c>
       <c r="G54" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J54" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1320</v>
+      </c>
+      <c r="L54" t="n">
+        <v>112</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.857</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:01.891</t>
+          <t>2026-05-29 09:35:05.976</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421683962</v>
+        <v>1780022104856</v>
       </c>
       <c r="C55" t="n">
-        <v>87812</v>
+        <v>81338</v>
       </c>
       <c r="D55" t="n">
-        <v>-477.69</v>
+        <v>-396.77</v>
       </c>
       <c r="E55" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F55" t="n">
-        <v>2296</v>
+        <v>4618</v>
       </c>
       <c r="G55" t="n">
-        <v>93.45999999999999</v>
+        <v>221.54</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1119</v>
+      </c>
+      <c r="L55" t="n">
+        <v>106</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.889</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:01.936</t>
+          <t>2026-05-29 09:35:05.977</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421684164</v>
+        <v>1780022105055</v>
       </c>
       <c r="C56" t="n">
-        <v>87961</v>
+        <v>81578</v>
       </c>
       <c r="D56" t="n">
-        <v>-304.8</v>
+        <v>-136.93</v>
       </c>
       <c r="E56" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="F56" t="n">
-        <v>2296</v>
+        <v>1059</v>
       </c>
       <c r="G56" t="n">
-        <v>93.45999999999999</v>
+        <v>240.4</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K56" t="n">
+        <v>921</v>
+      </c>
+      <c r="L56" t="n">
+        <v>119</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:02.298</t>
+          <t>2026-05-29 09:35:06.417</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421684365</v>
+        <v>1780022105256</v>
       </c>
       <c r="C57" t="n">
-        <v>88166</v>
+        <v>81094</v>
       </c>
       <c r="D57" t="n">
-        <v>-84.56</v>
+        <v>-614.09</v>
       </c>
       <c r="E57" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="F57" t="n">
-        <v>2296</v>
+        <v>1059</v>
       </c>
       <c r="G57" t="n">
-        <v>93.45999999999999</v>
+        <v>240.4</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L57" t="n">
+        <v>105</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.831</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:02.299</t>
+          <t>2026-05-29 09:35:06.424</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421684567</v>
+        <v>1780022105455</v>
       </c>
       <c r="C58" t="n">
-        <v>87900</v>
+        <v>81526</v>
       </c>
       <c r="D58" t="n">
-        <v>-346.34</v>
+        <v>-151.38</v>
       </c>
       <c r="E58" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="F58" t="n">
-        <v>2296</v>
+        <v>1059</v>
       </c>
       <c r="G58" t="n">
-        <v>93.45999999999999</v>
+        <v>240.4</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>968</v>
+      </c>
+      <c r="L58" t="n">
+        <v>118</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.299</t>
+          <t>2026-05-29 09:35:06.426</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421684768</v>
+        <v>1780022105655</v>
       </c>
       <c r="C59" t="n">
-        <v>88273</v>
+        <v>82134</v>
       </c>
       <c r="D59" t="n">
-        <v>43.98</v>
+        <v>464.19</v>
       </c>
       <c r="E59" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F59" t="n">
-        <v>947</v>
+        <v>620</v>
       </c>
       <c r="G59" t="n">
-        <v>118.12</v>
+        <v>233.27</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K59" t="n">
+        <v>770</v>
+      </c>
+      <c r="L59" t="n">
+        <v>104</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.196</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.300</t>
+          <t>2026-05-29 09:35:06.984</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421684970</v>
+        <v>1780022105855</v>
       </c>
       <c r="C60" t="n">
-        <v>88438</v>
+        <v>81673</v>
       </c>
       <c r="D60" t="n">
-        <v>206.78</v>
+        <v>-20.02</v>
       </c>
       <c r="E60" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F60" t="n">
-        <v>947</v>
+        <v>620</v>
       </c>
       <c r="G60" t="n">
-        <v>118.12</v>
+        <v>233.27</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1128</v>
+      </c>
+      <c r="L60" t="n">
+        <v>110</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.546</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.301</t>
+          <t>2026-05-29 09:35:06.985</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421685171</v>
+        <v>1780022106055</v>
       </c>
       <c r="C61" t="n">
-        <v>88161</v>
+        <v>81859</v>
       </c>
       <c r="D61" t="n">
-        <v>-80.56</v>
+        <v>166.98</v>
       </c>
       <c r="E61" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F61" t="n">
-        <v>947</v>
+        <v>620</v>
       </c>
       <c r="G61" t="n">
-        <v>118.12</v>
+        <v>233.27</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>930</v>
+      </c>
+      <c r="L61" t="n">
+        <v>107</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.302</t>
+          <t>2026-05-29 09:35:07.210</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421685372</v>
+        <v>1780022106255</v>
       </c>
       <c r="C62" t="n">
-        <v>88334</v>
+        <v>82164</v>
       </c>
       <c r="D62" t="n">
-        <v>96.47</v>
+        <v>463.63</v>
       </c>
       <c r="E62" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F62" t="n">
-        <v>947</v>
+        <v>620</v>
       </c>
       <c r="G62" t="n">
-        <v>118.12</v>
+        <v>233.27</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K62" t="n">
+        <v>953</v>
+      </c>
+      <c r="L62" t="n">
+        <v>108</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.153</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.545</t>
+          <t>2026-05-29 09:35:07.211</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421685574</v>
+        <v>1780022106455</v>
       </c>
       <c r="C63" t="n">
-        <v>88822</v>
+        <v>81673</v>
       </c>
       <c r="D63" t="n">
-        <v>579.65</v>
+        <v>-50.55</v>
       </c>
       <c r="E63" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F63" t="n">
-        <v>745</v>
+        <v>620</v>
       </c>
       <c r="G63" t="n">
-        <v>114.63</v>
+        <v>233.27</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>755</v>
+      </c>
+      <c r="L63" t="n">
+        <v>103</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.018</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.545</t>
+          <t>2026-05-29 09:35:07.799</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421685775</v>
+        <v>1780022106655</v>
       </c>
       <c r="C64" t="n">
-        <v>88777</v>
+        <v>81938</v>
       </c>
       <c r="D64" t="n">
-        <v>505.66</v>
+        <v>216.98</v>
       </c>
       <c r="E64" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F64" t="n">
-        <v>745</v>
+        <v>620</v>
       </c>
       <c r="G64" t="n">
-        <v>114.63</v>
+        <v>233.27</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1141</v>
+      </c>
+      <c r="L64" t="n">
+        <v>126</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.301</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.959</t>
+          <t>2026-05-29 09:35:07.800</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421685977</v>
+        <v>1780022106855</v>
       </c>
       <c r="C65" t="n">
-        <v>88379</v>
+        <v>83411</v>
       </c>
       <c r="D65" t="n">
-        <v>82.38</v>
+        <v>1679.13</v>
       </c>
       <c r="E65" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F65" t="n">
-        <v>745</v>
+        <v>1300</v>
       </c>
       <c r="G65" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>944</v>
+      </c>
+      <c r="L65" t="n">
+        <v>110</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.974</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:03.982</t>
+          <t>2026-05-29 09:35:08.004</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421686178</v>
+        <v>1780022107074</v>
       </c>
       <c r="C66" t="n">
-        <v>88701</v>
+        <v>82858</v>
       </c>
       <c r="D66" t="n">
-        <v>400.26</v>
+        <v>1042.17</v>
       </c>
       <c r="E66" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F66" t="n">
-        <v>745</v>
+        <v>1300</v>
       </c>
       <c r="G66" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K66" t="n">
+        <v>929</v>
+      </c>
+      <c r="L66" t="n">
+        <v>111</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.796</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:04.367</t>
+          <t>2026-05-29 09:35:08.005</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421686379</v>
+        <v>1780022107274</v>
       </c>
       <c r="C67" t="n">
-        <v>89007</v>
+        <v>82796</v>
       </c>
       <c r="D67" t="n">
-        <v>686.25</v>
+        <v>928.0599999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F67" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G67" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>730</v>
+      </c>
+      <c r="L67" t="n">
+        <v>108</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.504</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:04.375</t>
+          <t>2026-05-29 09:35:08.449</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421686581</v>
+        <v>1780022107474</v>
       </c>
       <c r="C68" t="n">
-        <v>88615</v>
+        <v>83676</v>
       </c>
       <c r="D68" t="n">
-        <v>259.94</v>
+        <v>1761.66</v>
       </c>
       <c r="E68" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F68" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G68" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K68" t="n">
+        <v>974</v>
+      </c>
+      <c r="L68" t="n">
+        <v>110</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.095</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.224</t>
+          <t>2026-05-29 09:35:08.454</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421686782</v>
+        <v>1780022107674</v>
       </c>
       <c r="C69" t="n">
-        <v>88971</v>
+        <v>84900</v>
       </c>
       <c r="D69" t="n">
-        <v>602.9400000000001</v>
+        <v>2897.58</v>
       </c>
       <c r="E69" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F69" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G69" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>779</v>
+      </c>
+      <c r="L69" t="n">
+        <v>110</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.518</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.225</t>
+          <t>2026-05-29 09:35:09.175</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421686984</v>
+        <v>1780022107874</v>
       </c>
       <c r="C70" t="n">
-        <v>89127</v>
+        <v>85094</v>
       </c>
       <c r="D70" t="n">
-        <v>728.79</v>
+        <v>2946.7</v>
       </c>
       <c r="E70" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F70" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G70" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1299</v>
+      </c>
+      <c r="L70" t="n">
+        <v>114</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.983</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.242</t>
+          <t>2026-05-29 09:35:09.176</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421687185</v>
+        <v>1780022108074</v>
       </c>
       <c r="C71" t="n">
-        <v>89261</v>
+        <v>86413</v>
       </c>
       <c r="D71" t="n">
-        <v>826.35</v>
+        <v>4118.36</v>
       </c>
       <c r="E71" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F71" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G71" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1101</v>
+      </c>
+      <c r="L71" t="n">
+        <v>106</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.733</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.243</t>
+          <t>2026-05-29 09:35:10.223</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421687386</v>
+        <v>1780022108274</v>
       </c>
       <c r="C72" t="n">
-        <v>88785</v>
+        <v>86058</v>
       </c>
       <c r="D72" t="n">
-        <v>309.04</v>
+        <v>3557.44</v>
       </c>
       <c r="E72" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F72" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G72" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1948</v>
+      </c>
+      <c r="L72" t="n">
+        <v>112</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.598</t>
+          <t>2026-05-29 09:35:10.224</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421687588</v>
+        <v>1780022108474</v>
       </c>
       <c r="C73" t="n">
-        <v>88861</v>
+        <v>84873</v>
       </c>
       <c r="D73" t="n">
-        <v>369.58</v>
+        <v>2194.57</v>
       </c>
       <c r="E73" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F73" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G73" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1749</v>
+      </c>
+      <c r="L73" t="n">
+        <v>109</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.821</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.600</t>
+          <t>2026-05-29 09:35:10.225</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421687789</v>
+        <v>1780022108674</v>
       </c>
       <c r="C74" t="n">
-        <v>88932</v>
+        <v>84886</v>
       </c>
       <c r="D74" t="n">
-        <v>422.1</v>
+        <v>2097.84</v>
       </c>
       <c r="E74" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F74" t="n">
-        <v>766</v>
+        <v>1300</v>
       </c>
       <c r="G74" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1550</v>
+      </c>
+      <c r="L74" t="n">
+        <v>112</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.918</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.992</t>
+          <t>2026-05-29 09:35:10.227</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421687991</v>
+        <v>1780022108874</v>
       </c>
       <c r="C75" t="n">
-        <v>88910</v>
+        <v>85524</v>
       </c>
       <c r="D75" t="n">
-        <v>379</v>
+        <v>2630.95</v>
       </c>
       <c r="E75" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F75" t="n">
-        <v>1671</v>
+        <v>1300</v>
       </c>
       <c r="G75" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1352</v>
+      </c>
+      <c r="L75" t="n">
+        <v>108</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:05.993</t>
+          <t>2026-05-29 09:35:11.093</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421688192</v>
+        <v>1780022109093</v>
       </c>
       <c r="C76" t="n">
-        <v>88975</v>
+        <v>85689</v>
       </c>
       <c r="D76" t="n">
-        <v>425.05</v>
+        <v>2664.4</v>
       </c>
       <c r="E76" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F76" t="n">
-        <v>1671</v>
+        <v>1300</v>
       </c>
       <c r="G76" t="n">
-        <v>114.63</v>
+        <v>252.6</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1999</v>
+      </c>
+      <c r="L76" t="n">
+        <v>112</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.802</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.455</t>
+          <t>2026-05-29 09:35:11.095</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421688394</v>
+        <v>1780022109293</v>
       </c>
       <c r="C77" t="n">
-        <v>89109</v>
+        <v>85386</v>
       </c>
       <c r="D77" t="n">
-        <v>537.8</v>
+        <v>2228.18</v>
       </c>
       <c r="E77" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F77" t="n">
-        <v>444</v>
+        <v>1300</v>
       </c>
       <c r="G77" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J77" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1801</v>
+      </c>
+      <c r="L77" t="n">
+        <v>116</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.341</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.455</t>
+          <t>2026-05-29 09:35:11.097</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421688595</v>
+        <v>1780022109493</v>
       </c>
       <c r="C78" t="n">
-        <v>89401</v>
+        <v>85203</v>
       </c>
       <c r="D78" t="n">
-        <v>802.91</v>
+        <v>1933.77</v>
       </c>
       <c r="E78" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F78" t="n">
-        <v>444</v>
+        <v>1300</v>
       </c>
       <c r="G78" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J78" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1603</v>
+      </c>
+      <c r="L78" t="n">
+        <v>110</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.128</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.456</t>
+          <t>2026-05-29 09:35:11.742</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421688796</v>
+        <v>1780022109693</v>
       </c>
       <c r="C79" t="n">
-        <v>89173</v>
+        <v>85071</v>
       </c>
       <c r="D79" t="n">
-        <v>534.76</v>
+        <v>1705.09</v>
       </c>
       <c r="E79" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F79" t="n">
-        <v>444</v>
+        <v>1300</v>
       </c>
       <c r="G79" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J79" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2049</v>
+      </c>
+      <c r="L79" t="n">
+        <v>114</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.718</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.457</t>
+          <t>2026-05-29 09:35:11.759</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421688998</v>
+        <v>1780022110293</v>
       </c>
       <c r="C80" t="n">
-        <v>89444</v>
+        <v>85383</v>
       </c>
       <c r="D80" t="n">
-        <v>779.02</v>
+        <v>1931.83</v>
       </c>
       <c r="E80" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F80" t="n">
-        <v>444</v>
+        <v>1300</v>
       </c>
       <c r="G80" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1465</v>
+      </c>
+      <c r="L80" t="n">
+        <v>116</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.471</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.524</t>
+          <t>2026-05-29 09:35:11.761</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421689199</v>
+        <v>1780022110493</v>
       </c>
       <c r="C81" t="n">
-        <v>89307</v>
+        <v>85204</v>
       </c>
       <c r="D81" t="n">
-        <v>603.0700000000001</v>
+        <v>1656.24</v>
       </c>
       <c r="E81" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F81" t="n">
-        <v>444</v>
+        <v>1300</v>
       </c>
       <c r="G81" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1267</v>
+      </c>
+      <c r="L81" t="n">
+        <v>112</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.065</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.525</t>
+          <t>2026-05-29 09:35:11.772</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421689401</v>
+        <v>1780022110693</v>
       </c>
       <c r="C82" t="n">
-        <v>89225</v>
+        <v>86097</v>
       </c>
       <c r="D82" t="n">
-        <v>490.92</v>
+        <v>2466.43</v>
       </c>
       <c r="E82" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F82" t="n">
-        <v>444</v>
+        <v>3858</v>
       </c>
       <c r="G82" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L82" t="n">
+        <v>114</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.339</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.876</t>
+          <t>2026-05-29 09:35:12.121</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421689602</v>
+        <v>1780022110912</v>
       </c>
       <c r="C83" t="n">
-        <v>89292</v>
+        <v>85818</v>
       </c>
       <c r="D83" t="n">
-        <v>533.37</v>
+        <v>2064.11</v>
       </c>
       <c r="E83" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F83" t="n">
-        <v>444</v>
+        <v>3858</v>
       </c>
       <c r="G83" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1208</v>
+      </c>
+      <c r="L83" t="n">
+        <v>109</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.879</t>
+          <t>2026-05-29 09:35:12.123</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421689803</v>
+        <v>1780022111112</v>
       </c>
       <c r="C84" t="n">
-        <v>89291</v>
+        <v>85372</v>
       </c>
       <c r="D84" t="n">
-        <v>505.7</v>
+        <v>1514.9</v>
       </c>
       <c r="E84" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F84" t="n">
-        <v>444</v>
+        <v>3858</v>
       </c>
       <c r="G84" t="n">
-        <v>139.97</v>
+        <v>252.6</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L84" t="n">
+        <v>106</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:07.892</t>
+          <t>2026-05-29 09:35:12.125</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421690005</v>
+        <v>1780022111312</v>
       </c>
       <c r="C85" t="n">
-        <v>89194</v>
+        <v>84610</v>
       </c>
       <c r="D85" t="n">
-        <v>383.42</v>
+        <v>677.16</v>
       </c>
       <c r="E85" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F85" t="n">
-        <v>1430</v>
+        <v>3858</v>
       </c>
       <c r="G85" t="n">
-        <v>275.87</v>
+        <v>252.6</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>812</v>
+      </c>
+      <c r="L85" t="n">
+        <v>111</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.626</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:08.544</t>
+          <t>2026-05-29 09:35:12.803</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421690206</v>
+        <v>1780022111512</v>
       </c>
       <c r="C86" t="n">
-        <v>88645</v>
+        <v>83972</v>
       </c>
       <c r="D86" t="n">
-        <v>-184.75</v>
+        <v>5.3</v>
       </c>
       <c r="E86" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F86" t="n">
-        <v>1430</v>
+        <v>3858</v>
       </c>
       <c r="G86" t="n">
-        <v>275.87</v>
+        <v>252.6</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L86" t="n">
+        <v>116</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:08.545</t>
+          <t>2026-05-29 09:35:12.805</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421690408</v>
+        <v>1780022111712</v>
       </c>
       <c r="C87" t="n">
-        <v>88742</v>
+        <v>83151</v>
       </c>
       <c r="D87" t="n">
-        <v>-78.51000000000001</v>
+        <v>-815.97</v>
       </c>
       <c r="E87" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F87" t="n">
-        <v>1430</v>
+        <v>3858</v>
       </c>
       <c r="G87" t="n">
-        <v>275.87</v>
+        <v>252.6</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L87" t="n">
+        <v>115</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.002</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:08.546</t>
+          <t>2026-05-29 09:35:13.356</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421690609</v>
+        <v>1780022111912</v>
       </c>
       <c r="C88" t="n">
-        <v>88840</v>
+        <v>83363</v>
       </c>
       <c r="D88" t="n">
-        <v>23.41</v>
+        <v>-563.17</v>
       </c>
       <c r="E88" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F88" t="n">
-        <v>1430</v>
+        <v>3858</v>
       </c>
       <c r="G88" t="n">
-        <v>275.87</v>
+        <v>252.6</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1442</v>
+      </c>
+      <c r="L88" t="n">
+        <v>110</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.901</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:08.865</t>
+          <t>2026-05-29 09:35:13.358</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421690811</v>
+        <v>1780022112112</v>
       </c>
       <c r="C89" t="n">
-        <v>89094</v>
+        <v>83743</v>
       </c>
       <c r="D89" t="n">
-        <v>276.24</v>
+        <v>-155.01</v>
       </c>
       <c r="E89" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F89" t="n">
-        <v>1430</v>
+        <v>3858</v>
       </c>
       <c r="G89" t="n">
-        <v>275.87</v>
+        <v>252.6</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L89" t="n">
+        <v>111</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.664</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:08.865</t>
+          <t>2026-05-29 09:35:13.359</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421691012</v>
+        <v>1780022112312</v>
       </c>
       <c r="C90" t="n">
-        <v>88815</v>
+        <v>83701</v>
       </c>
       <c r="D90" t="n">
-        <v>-16.57</v>
+        <v>-189.26</v>
       </c>
       <c r="E90" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F90" t="n">
-        <v>1027</v>
+        <v>3858</v>
       </c>
       <c r="G90" t="n">
-        <v>288.65</v>
+        <v>252.6</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1046</v>
+      </c>
+      <c r="L90" t="n">
+        <v>114</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.355</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:09.277</t>
+          <t>2026-05-29 09:35:13.698</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421691213</v>
+        <v>1780022112512</v>
       </c>
       <c r="C91" t="n">
-        <v>89087</v>
+        <v>84120</v>
       </c>
       <c r="D91" t="n">
-        <v>256.26</v>
+        <v>239.2</v>
       </c>
       <c r="E91" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F91" t="n">
-        <v>1027</v>
+        <v>3858</v>
       </c>
       <c r="G91" t="n">
-        <v>288.65</v>
+        <v>252.6</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L91" t="n">
+        <v>111</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.115</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:09.298</t>
+          <t>2026-05-29 09:35:13.733</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421691415</v>
+        <v>1780022112712</v>
       </c>
       <c r="C92" t="n">
-        <v>89156</v>
+        <v>84874</v>
       </c>
       <c r="D92" t="n">
-        <v>312.44</v>
+        <v>981.24</v>
       </c>
       <c r="E92" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F92" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G92" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L92" t="n">
+        <v>108</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.717</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:09.686</t>
+          <t>2026-05-29 09:35:14.213</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421691616</v>
+        <v>1780022112931</v>
       </c>
       <c r="C93" t="n">
-        <v>88789</v>
+        <v>84828</v>
       </c>
       <c r="D93" t="n">
-        <v>-70.18000000000001</v>
+        <v>886.1799999999999</v>
       </c>
       <c r="E93" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F93" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G93" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L93" t="n">
+        <v>115</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.781</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:09.688</t>
+          <t>2026-05-29 09:35:14.235</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421691818</v>
+        <v>1780022113131</v>
       </c>
       <c r="C94" t="n">
-        <v>88814</v>
+        <v>86571</v>
       </c>
       <c r="D94" t="n">
-        <v>-41.67</v>
+        <v>2584.87</v>
       </c>
       <c r="E94" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F94" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G94" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1103</v>
+      </c>
+      <c r="L94" t="n">
+        <v>110</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:10.079</t>
+          <t>2026-05-29 09:35:15.087</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421692019</v>
+        <v>1780022113331</v>
       </c>
       <c r="C95" t="n">
-        <v>88833</v>
+        <v>85950</v>
       </c>
       <c r="D95" t="n">
-        <v>-20.59</v>
+        <v>1834.63</v>
       </c>
       <c r="E95" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F95" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G95" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1755</v>
+      </c>
+      <c r="L95" t="n">
+        <v>108</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:10.086</t>
+          <t>2026-05-29 09:35:15.089</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421692220</v>
+        <v>1780022113531</v>
       </c>
       <c r="C96" t="n">
-        <v>88681</v>
+        <v>85084</v>
       </c>
       <c r="D96" t="n">
-        <v>-171.56</v>
+        <v>876.9</v>
       </c>
       <c r="E96" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F96" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G96" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1556</v>
+      </c>
+      <c r="L96" t="n">
+        <v>106</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.117</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:10.714</t>
+          <t>2026-05-29 09:35:15.295</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421692422</v>
+        <v>1780022113731</v>
       </c>
       <c r="C97" t="n">
-        <v>88627</v>
+        <v>84959</v>
       </c>
       <c r="D97" t="n">
-        <v>-216.98</v>
+        <v>708.05</v>
       </c>
       <c r="E97" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F97" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G97" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1562</v>
+      </c>
+      <c r="L97" t="n">
+        <v>117</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.683</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:10.715</t>
+          <t>2026-05-29 09:35:15.296</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421692623</v>
+        <v>1780022113931</v>
       </c>
       <c r="C98" t="n">
-        <v>88666</v>
+        <v>83829</v>
       </c>
       <c r="D98" t="n">
-        <v>-167.13</v>
+        <v>-457.35</v>
       </c>
       <c r="E98" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F98" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G98" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L98" t="n">
+        <v>109</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.533</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:10.716</t>
+          <t>2026-05-29 09:35:15.297</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421692825</v>
+        <v>1780022114131</v>
       </c>
       <c r="C99" t="n">
-        <v>88749</v>
+        <v>84071</v>
       </c>
       <c r="D99" t="n">
-        <v>-75.77</v>
+        <v>-192.48</v>
       </c>
       <c r="E99" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F99" t="n">
-        <v>423</v>
+        <v>3858</v>
       </c>
       <c r="G99" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L99" t="n">
+        <v>111</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.117</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:11.120</t>
+          <t>2026-05-29 09:35:15.299</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421693026</v>
+        <v>1780022114331</v>
       </c>
       <c r="C100" t="n">
-        <v>88490</v>
+        <v>84161</v>
       </c>
       <c r="D100" t="n">
-        <v>-330.98</v>
+        <v>-92.86</v>
       </c>
       <c r="E100" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F100" t="n">
-        <v>1611</v>
+        <v>3858</v>
       </c>
       <c r="G100" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>967</v>
+      </c>
+      <c r="L100" t="n">
+        <v>113</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.031</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:11.121</t>
+          <t>2026-05-29 09:35:16.307</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421693227</v>
+        <v>1780022114531</v>
       </c>
       <c r="C101" t="n">
-        <v>88610</v>
+        <v>83763</v>
       </c>
       <c r="D101" t="n">
-        <v>-194.44</v>
+        <v>-486.22</v>
       </c>
       <c r="E101" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F101" t="n">
-        <v>1611</v>
+        <v>3858</v>
       </c>
       <c r="G101" t="n">
-        <v>307.39</v>
+        <v>252.6</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1774</v>
+      </c>
+      <c r="L101" t="n">
+        <v>106</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.297</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:11.529</t>
+          <t>2026-05-29 09:35:16.319</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421693429</v>
+        <v>1780022114731</v>
       </c>
       <c r="C102" t="n">
-        <v>88853</v>
+        <v>83913</v>
       </c>
       <c r="D102" t="n">
-        <v>58.29</v>
+        <v>-311.9</v>
       </c>
       <c r="E102" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F102" t="n">
-        <v>524</v>
+        <v>3858</v>
       </c>
       <c r="G102" t="n">
-        <v>316.62</v>
+        <v>252.6</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1587</v>
+      </c>
+      <c r="L102" t="n">
+        <v>124</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.662</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:11.530</t>
+          <t>2026-05-29 09:35:16.485</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421693630</v>
+        <v>1780022114950</v>
       </c>
       <c r="C103" t="n">
-        <v>88477</v>
+        <v>84318</v>
       </c>
       <c r="D103" t="n">
-        <v>-320.63</v>
+        <v>108.69</v>
       </c>
       <c r="E103" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F103" t="n">
-        <v>524</v>
+        <v>3858</v>
       </c>
       <c r="G103" t="n">
-        <v>316.62</v>
+        <v>252.6</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1533</v>
+      </c>
+      <c r="L103" t="n">
+        <v>115</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.763</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:11.926</t>
+          <t>2026-05-29 09:35:16.487</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421693832</v>
+        <v>1780022115150</v>
       </c>
       <c r="C104" t="n">
-        <v>88649</v>
+        <v>85404</v>
       </c>
       <c r="D104" t="n">
-        <v>-132.6</v>
+        <v>1189.26</v>
       </c>
       <c r="E104" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F104" t="n">
-        <v>524</v>
+        <v>3858</v>
       </c>
       <c r="G104" t="n">
-        <v>316.62</v>
+        <v>252.6</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1336</v>
+      </c>
+      <c r="L104" t="n">
+        <v>112</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:11.927</t>
+          <t>2026-05-29 09:35:16.488</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421694033</v>
+        <v>1780022115350</v>
       </c>
       <c r="C105" t="n">
-        <v>88859</v>
+        <v>85584</v>
       </c>
       <c r="D105" t="n">
-        <v>84.03</v>
+        <v>1309.79</v>
       </c>
       <c r="E105" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F105" t="n">
-        <v>524</v>
+        <v>3858</v>
       </c>
       <c r="G105" t="n">
-        <v>316.62</v>
+        <v>252.6</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1137</v>
+      </c>
+      <c r="L105" t="n">
+        <v>115</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.503</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:12.399</t>
+          <t>2026-05-29 09:35:16.488</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421694235</v>
+        <v>1780022115550</v>
       </c>
       <c r="C106" t="n">
-        <v>89075</v>
+        <v>85305</v>
       </c>
       <c r="D106" t="n">
-        <v>295.83</v>
+        <v>965.3</v>
       </c>
       <c r="E106" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="F106" t="n">
-        <v>644</v>
+        <v>3858</v>
       </c>
       <c r="G106" t="n">
-        <v>314.92</v>
+        <v>252.6</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K106" t="n">
+        <v>938</v>
+      </c>
+      <c r="L106" t="n">
+        <v>109</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.503</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:12.399</t>
+          <t>2026-05-29 09:35:17.189</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421694436</v>
+        <v>1780022115750</v>
       </c>
       <c r="C107" t="n">
-        <v>88762</v>
+        <v>84264</v>
       </c>
       <c r="D107" t="n">
-        <v>-31.96</v>
+        <v>-123.96</v>
       </c>
       <c r="E107" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="F107" t="n">
-        <v>644</v>
+        <v>3858</v>
       </c>
       <c r="G107" t="n">
-        <v>314.92</v>
+        <v>252.6</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L107" t="n">
+        <v>113</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.561</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:12.798</t>
+          <t>2026-05-29 09:35:17.241</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421694638</v>
+        <v>1780022115950</v>
       </c>
       <c r="C108" t="n">
-        <v>88906</v>
+        <v>83845</v>
       </c>
       <c r="D108" t="n">
-        <v>113.64</v>
+        <v>-536.76</v>
       </c>
       <c r="E108" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="F108" t="n">
-        <v>644</v>
+        <v>3858</v>
       </c>
       <c r="G108" t="n">
-        <v>314.92</v>
+        <v>252.6</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L108" t="n">
+        <v>113</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.671</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:12.803</t>
+          <t>2026-05-29 09:35:17.689</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421694839</v>
+        <v>1780022116150</v>
       </c>
       <c r="C109" t="n">
-        <v>89061</v>
+        <v>83990</v>
       </c>
       <c r="D109" t="n">
-        <v>262.96</v>
+        <v>-364.93</v>
       </c>
       <c r="E109" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="F109" t="n">
-        <v>725</v>
+        <v>3858</v>
       </c>
       <c r="G109" t="n">
-        <v>305.26</v>
+        <v>252.6</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1539</v>
+      </c>
+      <c r="L109" t="n">
+        <v>119</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.544</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:13.165</t>
+          <t>2026-05-29 09:35:17.690</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421695040</v>
+        <v>1780022116350</v>
       </c>
       <c r="C110" t="n">
-        <v>89292</v>
+        <v>84079</v>
       </c>
       <c r="D110" t="n">
-        <v>480.81</v>
+        <v>-257.68</v>
       </c>
       <c r="E110" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="F110" t="n">
-        <v>725</v>
+        <v>3858</v>
       </c>
       <c r="G110" t="n">
-        <v>305.26</v>
+        <v>252.6</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1339</v>
+      </c>
+      <c r="L110" t="n">
+        <v>106</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.611</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:13.166</t>
+          <t>2026-05-29 09:35:17.691</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421695242</v>
+        <v>1780022116550</v>
       </c>
       <c r="C111" t="n">
-        <v>88818</v>
+        <v>85743</v>
       </c>
       <c r="D111" t="n">
-        <v>-17.23</v>
+        <v>1419.2</v>
       </c>
       <c r="E111" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="F111" t="n">
-        <v>725</v>
+        <v>3858</v>
       </c>
       <c r="G111" t="n">
-        <v>305.26</v>
+        <v>252.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L111" t="n">
+        <v>108</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.634</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:13.567</t>
+          <t>2026-05-29 09:35:17.691</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421695443</v>
+        <v>1780022116769</v>
       </c>
       <c r="C112" t="n">
-        <v>88982</v>
+        <v>84583</v>
       </c>
       <c r="D112" t="n">
-        <v>147.63</v>
+        <v>188.24</v>
       </c>
       <c r="E112" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="F112" t="n">
-        <v>725</v>
+        <v>3858</v>
       </c>
       <c r="G112" t="n">
-        <v>305.26</v>
+        <v>252.6</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>922</v>
+      </c>
+      <c r="L112" t="n">
+        <v>110</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:13.572</t>
+          <t>2026-05-29 09:35:18.165</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421695645</v>
+        <v>1780022116969</v>
       </c>
       <c r="C113" t="n">
-        <v>89158</v>
+        <v>83993</v>
       </c>
       <c r="D113" t="n">
-        <v>316.25</v>
+        <v>-411.17</v>
       </c>
       <c r="E113" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F113" t="n">
-        <v>867</v>
+        <v>3858</v>
       </c>
       <c r="G113" t="n">
-        <v>301.05</v>
+        <v>252.6</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L113" t="n">
+        <v>116</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:13.976</t>
+          <t>2026-05-29 09:35:18.180</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421695846</v>
+        <v>1780022117169</v>
       </c>
       <c r="C114" t="n">
-        <v>89181</v>
+        <v>83724</v>
       </c>
       <c r="D114" t="n">
-        <v>323.44</v>
+        <v>-659.61</v>
       </c>
       <c r="E114" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F114" t="n">
-        <v>867</v>
+        <v>3858</v>
       </c>
       <c r="G114" t="n">
-        <v>301.05</v>
+        <v>252.6</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J114" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L114" t="n">
+        <v>111</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.668</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:13.977</t>
+          <t>2026-05-29 09:35:19.256</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421696047</v>
+        <v>1780022117369</v>
       </c>
       <c r="C115" t="n">
-        <v>88897</v>
+        <v>83303</v>
       </c>
       <c r="D115" t="n">
-        <v>23.26</v>
+        <v>-1047.63</v>
       </c>
       <c r="E115" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F115" t="n">
-        <v>867</v>
+        <v>3858</v>
       </c>
       <c r="G115" t="n">
-        <v>301.05</v>
+        <v>252.6</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1885</v>
+      </c>
+      <c r="L115" t="n">
+        <v>108</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.913</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:13.978</t>
+          <t>2026-05-29 09:35:19.257</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421696249</v>
+        <v>1780022117569</v>
       </c>
       <c r="C116" t="n">
-        <v>89032</v>
+        <v>83320</v>
       </c>
       <c r="D116" t="n">
-        <v>157.1</v>
+        <v>-978.25</v>
       </c>
       <c r="E116" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F116" t="n">
-        <v>867</v>
+        <v>3858</v>
       </c>
       <c r="G116" t="n">
-        <v>301.05</v>
+        <v>252.6</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1687</v>
+      </c>
+      <c r="L116" t="n">
+        <v>109</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.578</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:14.422</t>
+          <t>2026-05-29 09:35:19.510</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421696450</v>
+        <v>1780022117769</v>
       </c>
       <c r="C117" t="n">
-        <v>89225</v>
+        <v>84565</v>
       </c>
       <c r="D117" t="n">
-        <v>342.25</v>
+        <v>315.66</v>
       </c>
       <c r="E117" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F117" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G117" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1741</v>
+      </c>
+      <c r="L117" t="n">
+        <v>116</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:14.427</t>
+          <t>2026-05-29 09:35:19.512</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421696652</v>
+        <v>1780022117969</v>
       </c>
       <c r="C118" t="n">
-        <v>89102</v>
+        <v>84726</v>
       </c>
       <c r="D118" t="n">
-        <v>202.13</v>
+        <v>460.88</v>
       </c>
       <c r="E118" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F118" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G118" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1542</v>
+      </c>
+      <c r="L118" t="n">
+        <v>113</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:14.809</t>
+          <t>2026-05-29 09:35:19.513</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421696853</v>
+        <v>1780022118169</v>
       </c>
       <c r="C119" t="n">
-        <v>89061</v>
+        <v>83915</v>
       </c>
       <c r="D119" t="n">
-        <v>151.03</v>
+        <v>-373.16</v>
       </c>
       <c r="E119" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F119" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G119" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1343</v>
+      </c>
+      <c r="L119" t="n">
+        <v>108</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.847</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:14.850</t>
+          <t>2026-05-29 09:35:19.515</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779421697054</v>
+        <v>1780022118369</v>
       </c>
       <c r="C120" t="n">
-        <v>89156</v>
+        <v>82499</v>
       </c>
       <c r="D120" t="n">
-        <v>238.48</v>
+        <v>-1770.5</v>
       </c>
       <c r="E120" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F120" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G120" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L120" t="n">
+        <v>106</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.911</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:15.409</t>
+          <t>2026-05-29 09:35:19.811</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779421697256</v>
+        <v>1780022118569</v>
       </c>
       <c r="C121" t="n">
-        <v>89389</v>
+        <v>83477</v>
       </c>
       <c r="D121" t="n">
-        <v>459.55</v>
+        <v>-703.98</v>
       </c>
       <c r="E121" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F121" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G121" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1241</v>
+      </c>
+      <c r="L121" t="n">
+        <v>107</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.494</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:15.410</t>
+          <t>2026-05-29 09:35:19.814</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779421697457</v>
+        <v>1780022118769</v>
       </c>
       <c r="C122" t="n">
-        <v>89138</v>
+        <v>84207</v>
       </c>
       <c r="D122" t="n">
-        <v>185.57</v>
+        <v>61.22</v>
       </c>
       <c r="E122" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F122" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G122" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J122" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1044</v>
+      </c>
+      <c r="L122" t="n">
+        <v>116</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.145</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:15.411</t>
+          <t>2026-05-29 09:35:20.194</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779421697659</v>
+        <v>1780022118989</v>
       </c>
       <c r="C123" t="n">
-        <v>89040</v>
+        <v>83202</v>
       </c>
       <c r="D123" t="n">
-        <v>78.3</v>
+        <v>-946.84</v>
       </c>
       <c r="E123" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F123" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G123" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1204</v>
+      </c>
+      <c r="L123" t="n">
+        <v>106</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.272</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:15.847</t>
+          <t>2026-05-29 09:35:20.230</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779421697860</v>
+        <v>1780022119188</v>
       </c>
       <c r="C124" t="n">
-        <v>89168</v>
+        <v>84352</v>
       </c>
       <c r="D124" t="n">
-        <v>202.38</v>
+        <v>250.5</v>
       </c>
       <c r="E124" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F124" t="n">
-        <v>765</v>
+        <v>3858</v>
       </c>
       <c r="G124" t="n">
-        <v>301.01</v>
+        <v>252.6</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1041</v>
+      </c>
+      <c r="L124" t="n">
+        <v>109</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.175</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:15.860</t>
+          <t>2026-05-29 09:35:20.705</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779421698061</v>
+        <v>1780022119388</v>
       </c>
       <c r="C125" t="n">
-        <v>89316</v>
+        <v>84326</v>
       </c>
       <c r="D125" t="n">
-        <v>340.26</v>
+        <v>211.98</v>
       </c>
       <c r="E125" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F125" t="n">
-        <v>846</v>
+        <v>8575</v>
       </c>
       <c r="G125" t="n">
-        <v>280.02</v>
+        <v>252.6</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1315</v>
+      </c>
+      <c r="L125" t="n">
+        <v>114</v>
+      </c>
+      <c r="M125" t="n">
+        <v>2.588</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:16.500</t>
+          <t>2026-05-29 09:35:20.707</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779421698263</v>
+        <v>1780022119588</v>
       </c>
       <c r="C126" t="n">
-        <v>89124</v>
+        <v>83738</v>
       </c>
       <c r="D126" t="n">
-        <v>131.25</v>
+        <v>-386.62</v>
       </c>
       <c r="E126" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F126" t="n">
-        <v>846</v>
+        <v>8575</v>
       </c>
       <c r="G126" t="n">
-        <v>280.02</v>
+        <v>252.6</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1118</v>
+      </c>
+      <c r="L126" t="n">
+        <v>110</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.696</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:16.501</t>
+          <t>2026-05-29 09:35:20.709</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779421698464</v>
+        <v>1780022119788</v>
       </c>
       <c r="C127" t="n">
-        <v>89012</v>
+        <v>83106</v>
       </c>
       <c r="D127" t="n">
-        <v>12.69</v>
+        <v>-999.29</v>
       </c>
       <c r="E127" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F127" t="n">
-        <v>846</v>
+        <v>8575</v>
       </c>
       <c r="G127" t="n">
-        <v>280.02</v>
+        <v>252.6</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>920</v>
+      </c>
+      <c r="L127" t="n">
+        <v>114</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.332</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:16.503</t>
+          <t>2026-05-29 09:35:21.240</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779421698666</v>
+        <v>1780022119988</v>
       </c>
       <c r="C128" t="n">
-        <v>89082</v>
+        <v>83058</v>
       </c>
       <c r="D128" t="n">
-        <v>82.05</v>
+        <v>-997.33</v>
       </c>
       <c r="E128" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F128" t="n">
-        <v>846</v>
+        <v>8575</v>
       </c>
       <c r="G128" t="n">
-        <v>280.02</v>
+        <v>252.6</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L128" t="n">
+        <v>110</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:16.850</t>
+          <t>2026-05-29 09:35:21.241</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779421698867</v>
+        <v>1780022120188</v>
       </c>
       <c r="C129" t="n">
-        <v>89251</v>
+        <v>83600</v>
       </c>
       <c r="D129" t="n">
-        <v>246.95</v>
+        <v>-405.46</v>
       </c>
       <c r="E129" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F129" t="n">
-        <v>846</v>
+        <v>8575</v>
       </c>
       <c r="G129" t="n">
-        <v>280.02</v>
+        <v>252.6</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1052</v>
+      </c>
+      <c r="L129" t="n">
+        <v>103</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.983</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:16.851</t>
+          <t>2026-05-29 09:35:21.242</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779421699069</v>
+        <v>1780022120388</v>
       </c>
       <c r="C130" t="n">
-        <v>88799</v>
+        <v>83176</v>
       </c>
       <c r="D130" t="n">
-        <v>-217.4</v>
+        <v>-809.1900000000001</v>
       </c>
       <c r="E130" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F130" t="n">
-        <v>866</v>
+        <v>8575</v>
       </c>
       <c r="G130" t="n">
-        <v>177.38</v>
+        <v>252.6</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K130" t="n">
+        <v>853</v>
+      </c>
+      <c r="L130" t="n">
+        <v>115</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.285</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:17.257</t>
+          <t>2026-05-29 09:35:22.985</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779421699270</v>
+        <v>1780022120588</v>
       </c>
       <c r="C131" t="n">
-        <v>88968</v>
+        <v>83436</v>
       </c>
       <c r="D131" t="n">
-        <v>-37.53</v>
+        <v>-508.73</v>
       </c>
       <c r="E131" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F131" t="n">
-        <v>866</v>
+        <v>8575</v>
       </c>
       <c r="G131" t="n">
-        <v>177.38</v>
+        <v>252.6</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K131" t="n">
+        <v>2396</v>
+      </c>
+      <c r="L131" t="n">
+        <v>114</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.883</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:17.257</t>
+          <t>2026-05-29 09:35:22.986</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779421699471</v>
+        <v>1780022120788</v>
       </c>
       <c r="C132" t="n">
-        <v>89120</v>
+        <v>83390</v>
       </c>
       <c r="D132" t="n">
-        <v>116.35</v>
+        <v>-529.29</v>
       </c>
       <c r="E132" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F132" t="n">
-        <v>866</v>
+        <v>8575</v>
       </c>
       <c r="G132" t="n">
-        <v>177.38</v>
+        <v>252.6</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>2197</v>
+      </c>
+      <c r="L132" t="n">
+        <v>112</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.141</t>
+          <t>2026-05-29 09:35:22.995</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779421699673</v>
+        <v>1780022121007</v>
       </c>
       <c r="C133" t="n">
-        <v>89331</v>
+        <v>83532</v>
       </c>
       <c r="D133" t="n">
-        <v>321.53</v>
+        <v>-360.83</v>
       </c>
       <c r="E133" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F133" t="n">
-        <v>705</v>
+        <v>1560</v>
       </c>
       <c r="G133" t="n">
-        <v>147.2</v>
+        <v>252.6</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1987</v>
+      </c>
+      <c r="L133" t="n">
+        <v>112</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.655</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.147</t>
+          <t>2026-05-29 09:35:22.995</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779421699874</v>
+        <v>1780022121207</v>
       </c>
       <c r="C134" t="n">
-        <v>88876</v>
+        <v>84008</v>
       </c>
       <c r="D134" t="n">
-        <v>-149.55</v>
+        <v>133.21</v>
       </c>
       <c r="E134" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F134" t="n">
-        <v>705</v>
+        <v>1560</v>
       </c>
       <c r="G134" t="n">
-        <v>147.2</v>
+        <v>252.6</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1788</v>
+      </c>
+      <c r="L134" t="n">
+        <v>109</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.792</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.148</t>
+          <t>2026-05-29 09:35:22.999</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779421700076</v>
+        <v>1780022121407</v>
       </c>
       <c r="C135" t="n">
-        <v>89020</v>
+        <v>84262</v>
       </c>
       <c r="D135" t="n">
-        <v>1.93</v>
+        <v>380.55</v>
       </c>
       <c r="E135" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F135" t="n">
-        <v>705</v>
+        <v>1560</v>
       </c>
       <c r="G135" t="n">
-        <v>147.2</v>
+        <v>252.6</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1591</v>
+      </c>
+      <c r="L135" t="n">
+        <v>111</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.059</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.149</t>
+          <t>2026-05-29 09:35:23.052</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779421700277</v>
+        <v>1780022121607</v>
       </c>
       <c r="C136" t="n">
-        <v>89151</v>
+        <v>83737</v>
       </c>
       <c r="D136" t="n">
-        <v>132.83</v>
+        <v>-163.47</v>
       </c>
       <c r="E136" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F136" t="n">
-        <v>705</v>
+        <v>1560</v>
       </c>
       <c r="G136" t="n">
-        <v>147.2</v>
+        <v>252.6</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1444</v>
+      </c>
+      <c r="L136" t="n">
+        <v>114</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.221</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.484</t>
+          <t>2026-05-29 09:35:23.112</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779421700478</v>
+        <v>1780022121807</v>
       </c>
       <c r="C137" t="n">
-        <v>89320</v>
+        <v>84398</v>
       </c>
       <c r="D137" t="n">
-        <v>295.19</v>
+        <v>505.7</v>
       </c>
       <c r="E137" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F137" t="n">
-        <v>786</v>
+        <v>1560</v>
       </c>
       <c r="G137" t="n">
-        <v>107.01</v>
+        <v>252.6</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L137" t="n">
+        <v>110</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.635</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.485</t>
+          <t>2026-05-29 09:35:23.114</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779421700680</v>
+        <v>1780022122007</v>
       </c>
       <c r="C138" t="n">
-        <v>88765</v>
+        <v>82760</v>
       </c>
       <c r="D138" t="n">
-        <v>-274.57</v>
+        <v>-1157.59</v>
       </c>
       <c r="E138" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F138" t="n">
-        <v>786</v>
+        <v>1560</v>
       </c>
       <c r="G138" t="n">
-        <v>107.01</v>
+        <v>252.6</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J138" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1106</v>
+      </c>
+      <c r="L138" t="n">
+        <v>110</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.179</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.906</t>
+          <t>2026-05-29 09:35:23.385</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779421700881</v>
+        <v>1780022122207</v>
       </c>
       <c r="C139" t="n">
-        <v>88871</v>
+        <v>80819</v>
       </c>
       <c r="D139" t="n">
-        <v>-154.84</v>
+        <v>-3040.71</v>
       </c>
       <c r="E139" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F139" t="n">
-        <v>786</v>
+        <v>1560</v>
       </c>
       <c r="G139" t="n">
-        <v>107.01</v>
+        <v>252.6</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1176</v>
+      </c>
+      <c r="L139" t="n">
+        <v>123</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.304</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:18.907</t>
+          <t>2026-05-29 09:35:23.411</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779421701083</v>
+        <v>1780022122407</v>
       </c>
       <c r="C140" t="n">
-        <v>88924</v>
+        <v>83076</v>
       </c>
       <c r="D140" t="n">
-        <v>-94.09999999999999</v>
+        <v>-631.67</v>
       </c>
       <c r="E140" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F140" t="n">
-        <v>786</v>
+        <v>1560</v>
       </c>
       <c r="G140" t="n">
-        <v>107.01</v>
+        <v>252.6</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1003</v>
+      </c>
+      <c r="L140" t="n">
+        <v>109</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.115</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:19.309</t>
+          <t>2026-05-29 09:35:24.897</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779421701284</v>
+        <v>1780022122607</v>
       </c>
       <c r="C141" t="n">
-        <v>89051</v>
+        <v>83039</v>
       </c>
       <c r="D141" t="n">
-        <v>37.61</v>
+        <v>-637.09</v>
       </c>
       <c r="E141" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F141" t="n">
-        <v>786</v>
+        <v>1560</v>
       </c>
       <c r="G141" t="n">
-        <v>107.01</v>
+        <v>252.6</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:19.309</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779421701485</v>
-      </c>
-      <c r="C142" t="n">
-        <v>88602</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-413.27</v>
-      </c>
-      <c r="E142" t="n">
-        <v>73</v>
-      </c>
-      <c r="F142" t="n">
-        <v>946</v>
-      </c>
-      <c r="G142" t="n">
-        <v>90.18000000000001</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:19.784</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779421701687</v>
-      </c>
-      <c r="C143" t="n">
-        <v>88699</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-295.61</v>
-      </c>
-      <c r="E143" t="n">
-        <v>73</v>
-      </c>
-      <c r="F143" t="n">
-        <v>946</v>
-      </c>
-      <c r="G143" t="n">
-        <v>90.18000000000001</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:19.794</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779421701888</v>
-      </c>
-      <c r="C144" t="n">
-        <v>88778</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-201.83</v>
-      </c>
-      <c r="E144" t="n">
-        <v>73</v>
-      </c>
-      <c r="F144" t="n">
-        <v>946</v>
-      </c>
-      <c r="G144" t="n">
-        <v>90.18000000000001</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:20.129</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779421702090</v>
-      </c>
-      <c r="C145" t="n">
-        <v>88864</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-105.74</v>
-      </c>
-      <c r="E145" t="n">
-        <v>73</v>
-      </c>
-      <c r="F145" t="n">
-        <v>946</v>
-      </c>
-      <c r="G145" t="n">
-        <v>90.18000000000001</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:20.140</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779421702291</v>
-      </c>
-      <c r="C146" t="n">
-        <v>88404</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-560.45</v>
-      </c>
-      <c r="E146" t="n">
-        <v>75</v>
-      </c>
-      <c r="F146" t="n">
-        <v>786</v>
-      </c>
-      <c r="G146" t="n">
-        <v>74.12</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:20.556</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779421702492</v>
-      </c>
-      <c r="C147" t="n">
-        <v>88586</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-350.43</v>
-      </c>
-      <c r="E147" t="n">
-        <v>75</v>
-      </c>
-      <c r="F147" t="n">
-        <v>786</v>
-      </c>
-      <c r="G147" t="n">
-        <v>74.12</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:20.557</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779421702694</v>
-      </c>
-      <c r="C148" t="n">
-        <v>88679</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-239.91</v>
-      </c>
-      <c r="E148" t="n">
-        <v>75</v>
-      </c>
-      <c r="F148" t="n">
-        <v>786</v>
-      </c>
-      <c r="G148" t="n">
-        <v>74.12</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:20.959</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779421702895</v>
-      </c>
-      <c r="C149" t="n">
-        <v>88882</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-24.91</v>
-      </c>
-      <c r="E149" t="n">
-        <v>75</v>
-      </c>
-      <c r="F149" t="n">
-        <v>705</v>
-      </c>
-      <c r="G149" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:20.971</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779421703097</v>
-      </c>
-      <c r="C150" t="n">
-        <v>88306</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-599.67</v>
-      </c>
-      <c r="E150" t="n">
-        <v>75</v>
-      </c>
-      <c r="F150" t="n">
-        <v>705</v>
-      </c>
-      <c r="G150" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:21.356</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779421703298</v>
-      </c>
-      <c r="C151" t="n">
-        <v>88473</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-402.68</v>
-      </c>
-      <c r="E151" t="n">
-        <v>75</v>
-      </c>
-      <c r="F151" t="n">
-        <v>705</v>
-      </c>
-      <c r="G151" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:21.357</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779421703499</v>
-      </c>
-      <c r="C152" t="n">
-        <v>88649</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-206.55</v>
-      </c>
-      <c r="E152" t="n">
-        <v>75</v>
-      </c>
-      <c r="F152" t="n">
-        <v>705</v>
-      </c>
-      <c r="G152" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:22.174</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1779421703701</v>
-      </c>
-      <c r="C153" t="n">
-        <v>88811</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-34.22</v>
-      </c>
-      <c r="E153" t="n">
-        <v>75</v>
-      </c>
-      <c r="F153" t="n">
-        <v>785</v>
-      </c>
-      <c r="G153" t="n">
-        <v>73.56</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I141" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2289</v>
+      </c>
+      <c r="L141" t="n">
+        <v>109</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.254</v>
       </c>
     </row>
   </sheetData>
